--- a/GMAX0505/Карта регистров.xlsx
+++ b/GMAX0505/Карта регистров.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20384"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VPL\LabView_PRJ\GMAX0505\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agest\Downloads\Telegram Desktop\GMAX0505_LV\GMAX0505\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2EB9F0-D625-472C-8455-4131E087CF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB000F7-34E1-4E44-8CA6-DA7CAD82413F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="80">
   <si>
     <t>Регистр</t>
   </si>
@@ -186,9 +186,6 @@
     <t>WR, 0d</t>
   </si>
   <si>
-    <t>???</t>
-  </si>
-  <si>
     <t>F4</t>
   </si>
   <si>
@@ -241,6 +238,34 @@
   </si>
   <si>
     <t>7F</t>
+  </si>
+  <si>
+    <t>0 бит = 1 стриминг</t>
+  </si>
+  <si>
+    <t>Internal EXP</t>
+  </si>
+  <si>
+    <t>*20</t>
+  </si>
+  <si>
+    <t>Тренировочный паттерн = 100001101110
+Выводится после STREAM_EN = 1</t>
+  </si>
+  <si>
+    <t>Особые настройки</t>
+  </si>
+  <si>
+    <t>Два канала</t>
+  </si>
+  <si>
+    <t>7 бит включает тест</t>
+  </si>
+  <si>
+    <t>Делим на 8</t>
+  </si>
+  <si>
+    <t>Темпа</t>
   </si>
 </sst>
 </file>
@@ -265,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,7 +299,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -299,43 +330,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -612,17 +634,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M257"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
+    <col min="12" max="12" width="2.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -641,16 +666,19 @@
       <c r="F1" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="H1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
+      <c r="B2" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -659,15 +687,21 @@
         <f>HEX2DEC(C2)</f>
         <v>160</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>23</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="5">
         <f>HEX2DEC(E2)</f>
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -678,15 +712,15 @@
         <f t="shared" ref="D3:D66" si="0">HEX2DEC(C3)</f>
         <v>5</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>5</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <f t="shared" ref="F3:F66" si="1">HEX2DEC(E3)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -697,15 +731,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -716,15 +750,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="5">
         <f t="shared" si="1"/>
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -735,15 +769,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>1</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -754,15 +788,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -773,20 +807,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -797,20 +831,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -821,20 +855,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -845,20 +879,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -869,20 +903,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -893,20 +927,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="5">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -917,20 +951,20 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>22</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -941,20 +975,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>14</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -965,20 +999,20 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -989,20 +1023,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="5">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1013,20 +1047,20 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E18" s="5">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1037,15 +1071,21 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>2</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G19" s="6">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1056,15 +1096,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="5">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1075,15 +1115,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>4</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="5">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1094,15 +1134,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="5">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1113,15 +1153,15 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1132,15 +1172,15 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>14</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1151,15 +1191,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="5">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1170,15 +1210,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="5">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1189,15 +1229,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="5">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1208,15 +1248,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="5">
-        <v>0</v>
-      </c>
-      <c r="F28" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1227,15 +1267,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="5">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1246,15 +1286,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E30" s="5">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1265,15 +1305,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E31" s="5">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1284,15 +1324,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E32" s="5">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1303,15 +1343,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E33" s="5">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1322,15 +1362,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E34" s="5">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -1341,15 +1381,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E35" s="5">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -1360,15 +1400,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E36" s="5">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -1379,15 +1419,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E37" s="5">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -1398,15 +1438,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E38" s="5">
-        <v>0</v>
-      </c>
-      <c r="F38" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -1417,15 +1457,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E39" s="5">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -1436,15 +1476,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E40" s="5">
-        <v>0</v>
-      </c>
-      <c r="F40" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -1455,15 +1495,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E41" s="5">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -1474,15 +1514,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E42" s="5">
-        <v>0</v>
-      </c>
-      <c r="F42" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -1493,15 +1533,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E43" s="5">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -1512,15 +1552,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E44" s="5">
-        <v>0</v>
-      </c>
-      <c r="F44" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -1531,15 +1571,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E45" s="5">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -1550,15 +1590,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E46" s="5">
-        <v>0</v>
-      </c>
-      <c r="F46" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -1569,15 +1609,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E47" s="5">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -1588,15 +1628,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E48" s="5">
-        <v>0</v>
-      </c>
-      <c r="F48" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -1607,15 +1647,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E49" s="5">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E49" s="4">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -1626,15 +1666,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E50" s="5">
-        <v>0</v>
-      </c>
-      <c r="F50" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -1645,15 +1685,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E51" s="5">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E51" s="4">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -1664,15 +1704,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E52" s="5">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -1683,15 +1723,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E53" s="5">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -1702,15 +1742,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E54" s="5">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -1721,15 +1761,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E55" s="5">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -1740,15 +1780,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E56" s="5">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -1759,15 +1799,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E57" s="5">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -1778,15 +1818,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E58" s="5">
-        <v>0</v>
-      </c>
-      <c r="F58" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -1797,15 +1837,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E59" s="5">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -1816,15 +1856,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E60" s="5">
-        <v>0</v>
-      </c>
-      <c r="F60" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -1835,15 +1875,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E61" s="5">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E61" s="4">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -1854,15 +1894,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E62" s="5">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -1873,15 +1913,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E63" s="5">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -1892,15 +1932,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E64" s="5">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E64" s="4">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -1911,15 +1951,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E65" s="5">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E65" s="4">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -1930,15 +1970,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E66" s="5">
-        <v>0</v>
-      </c>
-      <c r="F66" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -1949,15 +1989,15 @@
         <f t="shared" ref="D67:D130" si="2">HEX2DEC(C67)</f>
         <v>0</v>
       </c>
-      <c r="E67" s="5">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5">
+      <c r="E67" s="4">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4">
         <f t="shared" ref="F67:F130" si="3">HEX2DEC(E67)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -1968,15 +2008,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E68" s="5">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -1987,15 +2027,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E69" s="5">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E69" s="4">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -2006,15 +2046,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E70" s="5">
-        <v>0</v>
-      </c>
-      <c r="F70" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E70" s="4">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -2025,15 +2065,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E71" s="5">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E71" s="4">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -2044,15 +2084,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E72" s="5">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E72" s="4">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -2063,15 +2103,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E73" s="5">
-        <v>0</v>
-      </c>
-      <c r="F73" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E73" s="4">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -2082,15 +2122,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E74" s="5">
-        <v>0</v>
-      </c>
-      <c r="F74" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E74" s="4">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -2101,15 +2141,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E75" s="5">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E75" s="4">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -2120,15 +2160,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E76" s="5">
-        <v>0</v>
-      </c>
-      <c r="F76" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -2139,15 +2179,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E77" s="5">
-        <v>0</v>
-      </c>
-      <c r="F77" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E77" s="4">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -2158,15 +2198,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E78" s="5">
-        <v>0</v>
-      </c>
-      <c r="F78" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E78" s="4">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -2177,15 +2217,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E79" s="5">
-        <v>0</v>
-      </c>
-      <c r="F79" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E79" s="4">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -2196,15 +2236,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E80" s="5">
-        <v>0</v>
-      </c>
-      <c r="F80" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -2215,15 +2255,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E81" s="5">
-        <v>0</v>
-      </c>
-      <c r="F81" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E81" s="4">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -2234,15 +2274,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E82" s="5">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E82" s="4">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -2253,15 +2293,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E83" s="5">
-        <v>0</v>
-      </c>
-      <c r="F83" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E83" s="4">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -2272,15 +2312,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E84" s="5">
-        <v>0</v>
-      </c>
-      <c r="F84" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E84" s="4">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -2291,15 +2331,15 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="4">
         <v>32</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="4">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -2310,15 +2350,15 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="E86" s="5">
+      <c r="E86" s="4">
         <v>14</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="4">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -2329,15 +2369,15 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="E87" s="5">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -2348,15 +2388,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E88" s="5">
-        <v>0</v>
-      </c>
-      <c r="F88" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -2367,15 +2407,15 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E89" s="4">
         <v>6</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="5">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -2386,15 +2426,15 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="4">
         <v>2</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="4">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -2405,15 +2445,15 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="4">
         <v>2</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="4">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -2424,15 +2464,15 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E92" s="4">
         <v>4</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="4">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -2443,15 +2483,15 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="4">
         <v>4</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="4">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -2462,15 +2502,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E94" s="5">
-        <v>0</v>
-      </c>
-      <c r="F94" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -2481,15 +2521,15 @@
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E95" s="4">
         <v>20</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95" s="4">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -2500,15 +2540,15 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E96" s="4">
         <v>23</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="4">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -2519,15 +2559,15 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E97" s="4">
         <v>1</v>
       </c>
-      <c r="F97" s="5">
+      <c r="F97" s="4">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -2538,15 +2578,15 @@
         <f t="shared" si="2"/>
         <v>212</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F98" s="3">
+      <c r="E98" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" s="5">
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -2557,15 +2597,15 @@
         <f t="shared" si="2"/>
         <v>211</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="4">
         <v>35</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="5">
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -2576,15 +2616,15 @@
         <f t="shared" si="2"/>
         <v>198</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="E100" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F100" s="5">
         <f t="shared" si="3"/>
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -2595,15 +2635,15 @@
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="E101" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="E101" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F101" s="5">
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -2614,15 +2654,15 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="E102" s="5">
+      <c r="E102" s="4">
         <v>35</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="5">
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -2633,15 +2673,15 @@
         <f t="shared" si="2"/>
         <v>252</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E103" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F103" s="5">
+      <c r="F103" s="4">
         <f t="shared" si="3"/>
         <v>252</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -2652,15 +2692,15 @@
         <f t="shared" si="2"/>
         <v>255</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="4">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -2671,15 +2711,15 @@
         <f t="shared" si="2"/>
         <v>255</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="4">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -2690,15 +2730,15 @@
         <f t="shared" si="2"/>
         <v>255</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E106" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="4">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -2709,15 +2749,15 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E107" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107" s="5">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -2728,15 +2768,15 @@
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E108" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108" s="5">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -2747,15 +2787,15 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E109" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="5">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -2766,15 +2806,15 @@
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E110" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="5">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -2785,15 +2825,15 @@
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E111" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111" s="5">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -2804,15 +2844,15 @@
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="E112" s="5">
+      <c r="E112" s="4">
         <v>34</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112" s="5">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -2823,15 +2863,15 @@
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F113" s="3">
+      <c r="E113" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F113" s="5">
         <f t="shared" si="3"/>
         <v>216</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -2842,15 +2882,15 @@
         <f t="shared" si="2"/>
         <v>208</v>
       </c>
-      <c r="E114" s="5">
+      <c r="E114" s="4">
         <v>10</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="5">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -2861,15 +2901,15 @@
         <f t="shared" si="2"/>
         <v>201</v>
       </c>
-      <c r="E115" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F115" s="3">
+      <c r="E115" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F115" s="5">
         <f t="shared" si="3"/>
         <v>79</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -2880,15 +2920,15 @@
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="5">
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -2899,15 +2939,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E117" s="5">
-        <v>0</v>
-      </c>
-      <c r="F117" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E117" s="4">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -2918,15 +2958,15 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="E118" s="5">
+      <c r="E118" s="4">
         <v>8</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="5">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -2937,15 +2977,15 @@
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="E119" s="5">
+      <c r="E119" s="4">
         <v>90</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119" s="4">
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -2956,15 +2996,15 @@
         <f t="shared" si="2"/>
         <v>192</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="E120" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="4">
         <f t="shared" si="3"/>
         <v>192</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -2975,15 +3015,15 @@
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="E121" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F121" s="3">
+      <c r="E121" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F121" s="5">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -2994,15 +3034,15 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="E122" s="5">
+      <c r="E122" s="4">
         <v>9</v>
       </c>
-      <c r="F122" s="5">
+      <c r="F122" s="4">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -3013,15 +3053,15 @@
         <f t="shared" si="2"/>
         <v>172</v>
       </c>
-      <c r="E123" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F123" s="3">
+      <c r="E123" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F123" s="5">
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -3032,15 +3072,15 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="E124" s="5">
+      <c r="E124" s="4">
         <v>32</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="5">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -3051,15 +3091,15 @@
         <f t="shared" si="2"/>
         <v>199</v>
       </c>
-      <c r="E125" s="5" t="s">
+      <c r="E125" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125" s="5">
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -3070,15 +3110,15 @@
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="E126" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F126" s="3">
+      <c r="E126" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F126" s="5">
         <f t="shared" si="3"/>
         <v>91</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -3089,15 +3129,15 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="E127" s="5">
+      <c r="E127" s="4">
         <v>5</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="5">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -3108,15 +3148,15 @@
         <f t="shared" si="2"/>
         <v>156</v>
       </c>
-      <c r="E128" s="5" t="s">
+      <c r="E128" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="5">
         <f t="shared" si="3"/>
         <v>208</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -3127,15 +3167,15 @@
         <f t="shared" si="2"/>
         <v>208</v>
       </c>
-      <c r="E129" s="5" t="s">
+      <c r="E129" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="5">
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -3146,15 +3186,15 @@
         <f t="shared" si="2"/>
         <v>194</v>
       </c>
-      <c r="E130" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F130" s="3">
+      <c r="E130" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F130" s="5">
         <f t="shared" si="3"/>
         <v>195</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -3165,15 +3205,15 @@
         <f t="shared" ref="D131:D194" si="4">HEX2DEC(C131)</f>
         <v>60</v>
       </c>
-      <c r="E131" s="5">
+      <c r="E131" s="4">
         <v>44</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131" s="5">
         <f t="shared" ref="F131:F194" si="5">HEX2DEC(E131)</f>
         <v>68</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -3184,15 +3224,15 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E132" s="5">
+      <c r="E132" s="4">
         <v>2</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="5">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -3203,15 +3243,15 @@
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="E133" s="5">
+      <c r="E133" s="4">
         <v>10</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="5">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -3222,15 +3262,15 @@
         <f t="shared" si="4"/>
         <v>160</v>
       </c>
-      <c r="E134" s="5">
+      <c r="E134" s="4">
         <v>70</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134" s="5">
         <f t="shared" si="5"/>
         <v>112</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -3241,15 +3281,15 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E135" s="5">
+      <c r="E135" s="4">
         <v>43</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135" s="5">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -3260,15 +3300,15 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E136" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="5">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -3279,15 +3319,15 @@
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="E137" s="5">
+      <c r="E137" s="4">
         <v>30</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137" s="5">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -3298,15 +3338,15 @@
         <f t="shared" si="4"/>
         <v>156</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E138" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138" s="5">
         <f t="shared" si="5"/>
         <v>208</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -3317,15 +3357,15 @@
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="E139" s="5" t="s">
+      <c r="E139" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="4">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -3336,15 +3376,15 @@
         <f t="shared" si="4"/>
         <v>206</v>
       </c>
-      <c r="E140" s="5" t="s">
+      <c r="E140" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140" s="5">
         <f t="shared" si="5"/>
         <v>208</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -3355,15 +3395,15 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E141" s="5">
+      <c r="E141" s="4">
         <v>44</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141" s="5">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -3374,15 +3414,15 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="E142" s="5">
+      <c r="E142" s="4">
         <v>7</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142" s="5">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -3393,15 +3433,15 @@
         <f t="shared" si="4"/>
         <v>156</v>
       </c>
-      <c r="E143" s="5" t="s">
+      <c r="E143" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143" s="5">
         <f t="shared" si="5"/>
         <v>208</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -3412,15 +3452,15 @@
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="E144" s="5" t="s">
+      <c r="E144" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144" s="5">
         <f t="shared" si="5"/>
         <v>192</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -3431,15 +3471,15 @@
         <f t="shared" si="4"/>
         <v>194</v>
       </c>
-      <c r="E145" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F145" s="3">
+      <c r="E145" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F145" s="5">
         <f t="shared" si="5"/>
         <v>195</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -3450,15 +3490,15 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E146" s="5">
+      <c r="E146" s="4">
         <v>44</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="5">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -3469,15 +3509,15 @@
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="E147" s="5">
+      <c r="E147" s="4">
         <v>34</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="5">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -3488,15 +3528,15 @@
         <f t="shared" si="4"/>
         <v>188</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="E148" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148" s="5">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -3507,15 +3547,15 @@
         <f t="shared" si="4"/>
         <v>176</v>
       </c>
-      <c r="E149" s="5">
+      <c r="E149" s="4">
         <v>80</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149" s="5">
         <f t="shared" si="5"/>
         <v>128</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -3526,15 +3566,15 @@
         <f t="shared" si="4"/>
         <v>194</v>
       </c>
-      <c r="E150" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F150" s="3">
+      <c r="E150" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F150" s="5">
         <f t="shared" si="5"/>
         <v>195</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -3545,15 +3585,15 @@
         <f t="shared" si="4"/>
         <v>255</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="E151" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F151" s="5">
+      <c r="F151" s="4">
         <f t="shared" si="5"/>
         <v>255</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -3564,15 +3604,15 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="E152" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F152" s="5">
+      <c r="F152" s="4">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -3583,15 +3623,15 @@
         <f t="shared" si="4"/>
         <v>164</v>
       </c>
-      <c r="E153" s="5" t="s">
+      <c r="E153" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F153" s="5">
+      <c r="F153" s="4">
         <f t="shared" si="5"/>
         <v>164</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -3602,15 +3642,15 @@
         <f t="shared" si="4"/>
         <v>161</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="E154" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F154" s="5">
+      <c r="F154" s="4">
         <f t="shared" si="5"/>
         <v>161</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -3621,15 +3661,15 @@
         <f t="shared" si="4"/>
         <v>64</v>
       </c>
-      <c r="E155" s="5">
+      <c r="E155" s="4">
         <v>40</v>
       </c>
-      <c r="F155" s="5">
+      <c r="F155" s="4">
         <f t="shared" si="5"/>
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -3640,15 +3680,15 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="E156" s="5" t="s">
+      <c r="E156" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F156" s="5">
+      <c r="F156" s="4">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -3659,15 +3699,15 @@
         <f t="shared" si="4"/>
         <v>65</v>
       </c>
-      <c r="E157" s="5">
+      <c r="E157" s="4">
         <v>41</v>
       </c>
-      <c r="F157" s="5">
+      <c r="F157" s="4">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -3678,15 +3718,15 @@
         <f t="shared" si="4"/>
         <v>252</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E158" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F158" s="5">
+      <c r="F158" s="4">
         <f t="shared" si="5"/>
         <v>252</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -3697,15 +3737,15 @@
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E159" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F159" s="5">
+      <c r="F159" s="4">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -3716,15 +3756,15 @@
         <f t="shared" si="4"/>
         <v>129</v>
       </c>
-      <c r="E160" s="5">
+      <c r="E160" s="4">
         <v>81</v>
       </c>
-      <c r="F160" s="5">
+      <c r="F160" s="4">
         <f t="shared" si="5"/>
         <v>129</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -3735,15 +3775,15 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E161" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F161" s="5">
+      <c r="F161" s="4">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -3754,15 +3794,15 @@
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="E162" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F162" s="5">
+      <c r="F162" s="4">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -3773,15 +3813,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E163" s="5">
-        <v>0</v>
-      </c>
-      <c r="F163" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E163" s="4">
+        <v>0</v>
+      </c>
+      <c r="F163" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -3792,15 +3832,15 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="E164" s="5">
+      <c r="E164" s="4">
         <v>18</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164" s="5">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -3811,15 +3851,15 @@
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="E165" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F165" s="3">
+      <c r="E165" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F165" s="5">
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -3830,15 +3870,15 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="E166" s="5">
+      <c r="E166" s="4">
         <v>1</v>
       </c>
-      <c r="F166" s="5">
+      <c r="F166" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -3849,15 +3889,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E167" s="5">
-        <v>0</v>
-      </c>
-      <c r="F167" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E167" s="4">
+        <v>0</v>
+      </c>
+      <c r="F167" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -3868,15 +3908,15 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E168" s="5">
+      <c r="E168" s="4">
         <v>2</v>
       </c>
-      <c r="F168" s="5">
+      <c r="F168" s="4">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -3887,15 +3927,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E169" s="5">
-        <v>0</v>
-      </c>
-      <c r="F169" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E169" s="4">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -3906,15 +3946,15 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E170" s="5">
+      <c r="E170" s="4">
         <v>5</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170" s="4">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -3925,15 +3965,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E171" s="5">
-        <v>0</v>
-      </c>
-      <c r="F171" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E171" s="4">
+        <v>0</v>
+      </c>
+      <c r="F171" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -3944,15 +3984,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E172" s="5">
-        <v>0</v>
-      </c>
-      <c r="F172" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E172" s="4">
+        <v>0</v>
+      </c>
+      <c r="F172" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -3963,15 +4003,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E173" s="5">
-        <v>0</v>
-      </c>
-      <c r="F173" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E173" s="4">
+        <v>0</v>
+      </c>
+      <c r="F173" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -3982,15 +4022,15 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="E174" s="5">
+      <c r="E174" s="4">
         <v>7</v>
       </c>
-      <c r="F174" s="3">
+      <c r="F174" s="5">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -4001,15 +4041,15 @@
         <f t="shared" si="4"/>
         <v>156</v>
       </c>
-      <c r="E175" s="5" t="s">
+      <c r="E175" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F175" s="3">
+      <c r="F175" s="5">
         <f t="shared" si="5"/>
         <v>208</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -4020,15 +4060,15 @@
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="E176" s="5" t="s">
+      <c r="E176" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F176" s="3">
+      <c r="F176" s="5">
         <f t="shared" si="5"/>
         <v>192</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -4039,15 +4079,15 @@
         <f t="shared" si="4"/>
         <v>194</v>
       </c>
-      <c r="E177" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F177" s="3">
+      <c r="E177" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F177" s="5">
         <f t="shared" si="5"/>
         <v>195</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -4058,15 +4098,15 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E178" s="5">
+      <c r="E178" s="4">
         <v>44</v>
       </c>
-      <c r="F178" s="3">
+      <c r="F178" s="5">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -4077,15 +4117,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E179" s="5">
-        <v>0</v>
-      </c>
-      <c r="F179" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E179" s="4">
+        <v>0</v>
+      </c>
+      <c r="F179" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -4096,15 +4136,15 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="E180" s="5">
+      <c r="E180" s="4">
         <v>1</v>
       </c>
-      <c r="F180" s="5">
+      <c r="F180" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -4115,15 +4155,15 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="E181" s="5">
+      <c r="E181" s="4">
         <v>3</v>
       </c>
-      <c r="F181" s="3">
+      <c r="F181" s="5">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -4134,15 +4174,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E182" s="5">
-        <v>0</v>
-      </c>
-      <c r="F182" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E182" s="4">
+        <v>0</v>
+      </c>
+      <c r="F182" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -4153,15 +4193,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E183" s="5">
-        <v>0</v>
-      </c>
-      <c r="F183" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E183" s="4">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -4172,15 +4212,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E184" s="5">
-        <v>0</v>
-      </c>
-      <c r="F184" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E184" s="4">
+        <v>0</v>
+      </c>
+      <c r="F184" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -4191,15 +4231,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E185" s="5">
-        <v>0</v>
-      </c>
-      <c r="F185" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E185" s="4">
+        <v>0</v>
+      </c>
+      <c r="F185" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -4210,15 +4250,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E186" s="5">
-        <v>0</v>
-      </c>
-      <c r="F186" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E186" s="4">
+        <v>0</v>
+      </c>
+      <c r="F186" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -4229,15 +4269,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E187" s="5">
-        <v>0</v>
-      </c>
-      <c r="F187" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E187" s="4">
+        <v>0</v>
+      </c>
+      <c r="F187" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -4248,15 +4288,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E188" s="5">
-        <v>0</v>
-      </c>
-      <c r="F188" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E188" s="4">
+        <v>0</v>
+      </c>
+      <c r="F188" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -4267,15 +4307,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E189" s="5">
-        <v>0</v>
-      </c>
-      <c r="F189" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E189" s="4">
+        <v>0</v>
+      </c>
+      <c r="F189" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -4286,15 +4326,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E190" s="5">
-        <v>0</v>
-      </c>
-      <c r="F190" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E190" s="4">
+        <v>0</v>
+      </c>
+      <c r="F190" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -4305,15 +4345,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E191" s="5">
-        <v>0</v>
-      </c>
-      <c r="F191" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E191" s="4">
+        <v>0</v>
+      </c>
+      <c r="F191" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -4324,15 +4364,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E192" s="5">
-        <v>0</v>
-      </c>
-      <c r="F192" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E192" s="4">
+        <v>0</v>
+      </c>
+      <c r="F192" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -4343,15 +4383,15 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E193" s="5">
-        <v>0</v>
-      </c>
-      <c r="F193" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E193" s="4">
+        <v>0</v>
+      </c>
+      <c r="F193" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -4362,15 +4402,18 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E194" s="5">
-        <v>0</v>
-      </c>
-      <c r="F194" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E194" s="4">
+        <v>0</v>
+      </c>
+      <c r="F194" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -4381,15 +4424,16 @@
         <f t="shared" ref="D195:D257" si="6">HEX2DEC(C195)</f>
         <v>0</v>
       </c>
-      <c r="E195" s="5">
-        <v>0</v>
-      </c>
-      <c r="F195" s="5">
+      <c r="E195" s="4">
+        <v>0</v>
+      </c>
+      <c r="F195" s="4">
         <f t="shared" ref="F195:F257" si="7">HEX2DEC(E195)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G195" s="10"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -4400,15 +4444,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E196" s="5">
-        <v>0</v>
-      </c>
-      <c r="F196" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E196" s="4">
+        <v>0</v>
+      </c>
+      <c r="F196" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -4419,15 +4463,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E197" s="5">
-        <v>0</v>
-      </c>
-      <c r="F197" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E197" s="4">
+        <v>0</v>
+      </c>
+      <c r="F197" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -4438,15 +4482,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E198" s="5">
-        <v>0</v>
-      </c>
-      <c r="F198" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E198" s="4">
+        <v>0</v>
+      </c>
+      <c r="F198" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -4457,15 +4501,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E199" s="5">
-        <v>0</v>
-      </c>
-      <c r="F199" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E199" s="4">
+        <v>0</v>
+      </c>
+      <c r="F199" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -4476,15 +4520,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E200" s="5">
-        <v>0</v>
-      </c>
-      <c r="F200" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E200" s="4">
+        <v>0</v>
+      </c>
+      <c r="F200" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -4495,15 +4539,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E201" s="5">
-        <v>0</v>
-      </c>
-      <c r="F201" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E201" s="4">
+        <v>0</v>
+      </c>
+      <c r="F201" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -4514,15 +4558,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E202" s="5">
-        <v>0</v>
-      </c>
-      <c r="F202" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E202" s="4">
+        <v>0</v>
+      </c>
+      <c r="F202" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -4533,15 +4577,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E203" s="5">
-        <v>0</v>
-      </c>
-      <c r="F203" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E203" s="4">
+        <v>0</v>
+      </c>
+      <c r="F203" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -4552,15 +4596,15 @@
         <f t="shared" si="6"/>
         <v>176</v>
       </c>
-      <c r="E204" s="5" t="s">
+      <c r="E204" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F204" s="5">
+      <c r="F204" s="4">
         <f t="shared" si="7"/>
         <v>176</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -4571,15 +4615,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E205" s="5">
-        <v>0</v>
-      </c>
-      <c r="F205" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E205" s="4">
+        <v>0</v>
+      </c>
+      <c r="F205" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -4590,15 +4634,15 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="E206" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F206" s="3">
+      <c r="E206" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F206" s="5">
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -4609,15 +4653,15 @@
         <f t="shared" si="6"/>
         <v>161</v>
       </c>
-      <c r="E207" s="5">
+      <c r="E207" s="4">
         <v>21</v>
       </c>
-      <c r="F207" s="3">
+      <c r="F207" s="5">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -4628,15 +4672,15 @@
         <f t="shared" si="6"/>
         <v>128</v>
       </c>
-      <c r="E208" s="5">
+      <c r="E208" s="4">
         <v>80</v>
       </c>
-      <c r="F208" s="5">
+      <c r="F208" s="4">
         <f t="shared" si="7"/>
         <v>128</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -4647,15 +4691,21 @@
         <f t="shared" si="6"/>
         <v>241</v>
       </c>
-      <c r="E209" s="5" t="s">
+      <c r="E209" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F209" s="5">
+      <c r="F209" s="4">
         <f t="shared" si="7"/>
         <v>241</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G209" s="9">
+        <v>247</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -4666,15 +4716,15 @@
         <f t="shared" si="6"/>
         <v>131</v>
       </c>
-      <c r="E210" s="5">
+      <c r="E210" s="4">
         <v>83</v>
       </c>
-      <c r="F210" s="5">
+      <c r="F210" s="4">
         <f t="shared" si="7"/>
         <v>131</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -4685,15 +4735,16 @@
         <f t="shared" si="6"/>
         <v>208</v>
       </c>
-      <c r="E211" s="5">
+      <c r="E211" s="4">
         <v>80</v>
       </c>
-      <c r="F211" s="3">
+      <c r="F211" s="5">
         <f t="shared" si="7"/>
         <v>128</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H211" s="7"/>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -4704,15 +4755,21 @@
         <f t="shared" si="6"/>
         <v>151</v>
       </c>
-      <c r="E212" s="5">
+      <c r="E212" s="4">
         <v>95</v>
       </c>
-      <c r="F212" s="3">
+      <c r="F212" s="5">
         <f t="shared" si="7"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G212" s="9">
+        <v>165</v>
+      </c>
+      <c r="H212" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -4723,15 +4780,15 @@
         <f t="shared" si="6"/>
         <v>226</v>
       </c>
-      <c r="E213" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F213" s="3">
+      <c r="E213" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F213" s="5">
         <f t="shared" si="7"/>
         <v>204</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -4742,15 +4799,15 @@
         <f t="shared" si="6"/>
         <v>255</v>
       </c>
-      <c r="E214" s="5">
+      <c r="E214" s="4">
         <v>77</v>
       </c>
-      <c r="F214" s="3">
+      <c r="F214" s="5">
         <f t="shared" si="7"/>
         <v>119</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -4761,15 +4818,15 @@
         <f t="shared" si="6"/>
         <v>248</v>
       </c>
-      <c r="E215" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F215" s="3">
+      <c r="E215" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F215" s="5">
         <f t="shared" si="7"/>
         <v>243</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -4780,15 +4837,22 @@
         <f t="shared" si="6"/>
         <v>223</v>
       </c>
-      <c r="E216" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F216" s="3">
+      <c r="E216" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F216" s="5">
         <f t="shared" si="7"/>
         <v>221</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G216" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H216" s="10"/>
+      <c r="I216" s="10"/>
+      <c r="J216" s="10"/>
+      <c r="K216" s="10"/>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -4799,15 +4863,20 @@
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="E217" s="5" t="s">
+      <c r="E217" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F217" s="5">
+      <c r="F217" s="4">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G217" s="10"/>
+      <c r="H217" s="10"/>
+      <c r="I217" s="10"/>
+      <c r="J217" s="10"/>
+      <c r="K217" s="10"/>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -4818,15 +4887,20 @@
         <f t="shared" si="6"/>
         <v>247</v>
       </c>
-      <c r="E218" s="5" t="s">
+      <c r="E218" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F218" s="3">
+      <c r="F218" s="5">
         <f t="shared" si="7"/>
         <v>211</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G218" s="10"/>
+      <c r="H218" s="10"/>
+      <c r="I218" s="10"/>
+      <c r="J218" s="10"/>
+      <c r="K218" s="10"/>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -4837,15 +4911,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E219" s="5">
-        <v>0</v>
-      </c>
-      <c r="F219" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E219" s="4">
+        <v>0</v>
+      </c>
+      <c r="F219" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -4856,15 +4930,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E220" s="5">
-        <v>0</v>
-      </c>
-      <c r="F220" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E220" s="4">
+        <v>0</v>
+      </c>
+      <c r="F220" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -4875,15 +4949,15 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="E221" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F221" s="3">
+      <c r="E221" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F221" s="5">
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -4894,15 +4968,15 @@
         <f t="shared" si="6"/>
         <v>176</v>
       </c>
-      <c r="E222" s="5" t="s">
+      <c r="E222" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F222" s="5">
+      <c r="F222" s="4">
         <f t="shared" si="7"/>
         <v>176</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -4913,15 +4987,15 @@
         <f t="shared" si="6"/>
         <v>137</v>
       </c>
-      <c r="E223" s="5" t="s">
+      <c r="E223" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F223" s="3">
+      <c r="F223" s="5">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -4932,15 +5006,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E224" s="5" t="s">
+      <c r="E224" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F224" s="3">
+      <c r="F224" s="5">
         <f t="shared" si="7"/>
         <v>254</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -4951,15 +5025,15 @@
         <f t="shared" si="6"/>
         <v>98</v>
       </c>
-      <c r="E225" s="5">
+      <c r="E225" s="4">
         <v>62</v>
       </c>
-      <c r="F225" s="5">
+      <c r="F225" s="4">
         <f t="shared" si="7"/>
         <v>98</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -4970,15 +5044,15 @@
         <f t="shared" si="6"/>
         <v>191</v>
       </c>
-      <c r="E226" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F226" s="3">
+      <c r="E226" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F226" s="5">
         <f t="shared" si="7"/>
         <v>193</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -4989,15 +5063,15 @@
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="E227" s="5" t="s">
+      <c r="E227" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F227" s="5">
+      <c r="F227" s="4">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -5008,15 +5082,15 @@
         <f t="shared" si="6"/>
         <v>138</v>
       </c>
-      <c r="E228" s="5" t="s">
+      <c r="E228" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F228" s="5">
+      <c r="F228" s="4">
         <f t="shared" si="7"/>
         <v>138</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -5027,15 +5101,15 @@
         <f t="shared" si="6"/>
         <v>162</v>
       </c>
-      <c r="E229" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F229" s="3">
+      <c r="E229" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F229" s="5">
         <f t="shared" si="7"/>
         <v>202</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -5046,15 +5120,15 @@
         <f t="shared" si="6"/>
         <v>232</v>
       </c>
-      <c r="E230" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F230" s="3">
+      <c r="E230" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F230" s="5">
         <f t="shared" si="7"/>
         <v>231</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -5065,15 +5139,15 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="E231" s="5" t="s">
+      <c r="E231" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F231" s="3">
+      <c r="F231" s="5">
         <f t="shared" si="7"/>
         <v>168</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -5084,15 +5158,15 @@
         <f t="shared" si="6"/>
         <v>58</v>
       </c>
-      <c r="E232" s="5" t="s">
+      <c r="E232" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F232" s="3">
+      <c r="F232" s="5">
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -5103,15 +5177,15 @@
         <f t="shared" si="6"/>
         <v>138</v>
       </c>
-      <c r="E233" s="5" t="s">
+      <c r="E233" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F233" s="5">
+      <c r="F233" s="4">
         <f t="shared" si="7"/>
         <v>138</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -5122,15 +5196,15 @@
         <f t="shared" si="6"/>
         <v>254</v>
       </c>
-      <c r="E234" s="5" t="s">
+      <c r="E234" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F234" s="5">
+      <c r="F234" s="4">
         <f t="shared" si="7"/>
         <v>254</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -5141,15 +5215,15 @@
         <f t="shared" si="6"/>
         <v>126</v>
       </c>
-      <c r="E235" s="5">
+      <c r="E235" s="4">
         <v>82</v>
       </c>
-      <c r="F235" s="3">
+      <c r="F235" s="5">
         <f t="shared" si="7"/>
         <v>130</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>234</v>
       </c>
@@ -5160,15 +5234,15 @@
         <f t="shared" si="6"/>
         <v>252</v>
       </c>
-      <c r="E236" s="5">
+      <c r="E236" s="4">
         <v>34</v>
       </c>
-      <c r="F236" s="3">
+      <c r="F236" s="5">
         <f t="shared" si="7"/>
         <v>52</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -5179,15 +5253,15 @@
         <f t="shared" si="6"/>
         <v>126</v>
       </c>
-      <c r="E237" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F237" s="3">
+      <c r="E237" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F237" s="5">
         <f t="shared" si="7"/>
         <v>127</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -5198,15 +5272,15 @@
         <f t="shared" si="6"/>
         <v>191</v>
       </c>
-      <c r="E238" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F238" s="3">
+      <c r="E238" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F238" s="5">
         <f t="shared" si="7"/>
         <v>193</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -5217,15 +5291,15 @@
         <f t="shared" si="6"/>
         <v>159</v>
       </c>
-      <c r="E239" s="5">
+      <c r="E239" s="4">
         <v>20</v>
       </c>
-      <c r="F239" s="3">
+      <c r="F239" s="5">
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>238</v>
       </c>
@@ -5236,15 +5310,15 @@
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="E240" s="5">
+      <c r="E240" s="4">
         <v>2</v>
       </c>
-      <c r="F240" s="3">
+      <c r="F240" s="5">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -5255,15 +5329,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E241" s="5">
-        <v>0</v>
-      </c>
-      <c r="F241" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E241" s="4">
+        <v>0</v>
+      </c>
+      <c r="F241" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -5274,15 +5348,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E242" s="5">
-        <v>0</v>
-      </c>
-      <c r="F242" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E242" s="4">
+        <v>0</v>
+      </c>
+      <c r="F242" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -5293,15 +5367,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E243" s="5">
-        <v>0</v>
-      </c>
-      <c r="F243" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E243" s="4">
+        <v>0</v>
+      </c>
+      <c r="F243" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -5312,15 +5386,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E244" s="5">
-        <v>0</v>
-      </c>
-      <c r="F244" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E244" s="4">
+        <v>0</v>
+      </c>
+      <c r="F244" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -5331,15 +5405,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E245" s="5">
-        <v>0</v>
-      </c>
-      <c r="F245" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E245" s="4">
+        <v>0</v>
+      </c>
+      <c r="F245" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -5350,15 +5424,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E246" s="5">
-        <v>0</v>
-      </c>
-      <c r="F246" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E246" s="4">
+        <v>0</v>
+      </c>
+      <c r="F246" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -5369,15 +5443,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E247" s="5">
-        <v>0</v>
-      </c>
-      <c r="F247" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E247" s="4">
+        <v>0</v>
+      </c>
+      <c r="F247" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -5388,15 +5462,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E248" s="5">
-        <v>0</v>
-      </c>
-      <c r="F248" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E248" s="4">
+        <v>0</v>
+      </c>
+      <c r="F248" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -5407,15 +5481,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E249" s="5">
-        <v>0</v>
-      </c>
-      <c r="F249" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E249" s="4">
+        <v>0</v>
+      </c>
+      <c r="F249" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -5426,15 +5500,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E250" s="5">
-        <v>0</v>
-      </c>
-      <c r="F250" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E250" s="4">
+        <v>0</v>
+      </c>
+      <c r="F250" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -5445,15 +5519,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E251" s="5">
-        <v>0</v>
-      </c>
-      <c r="F251" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E251" s="4">
+        <v>0</v>
+      </c>
+      <c r="F251" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -5464,15 +5538,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E252" s="5">
-        <v>0</v>
-      </c>
-      <c r="F252" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E252" s="4">
+        <v>0</v>
+      </c>
+      <c r="F252" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -5483,15 +5557,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E253" s="5">
-        <v>0</v>
-      </c>
-      <c r="F253" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E253" s="4">
+        <v>0</v>
+      </c>
+      <c r="F253" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -5502,15 +5576,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E254" s="5">
-        <v>0</v>
-      </c>
-      <c r="F254" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E254" s="4">
+        <v>0</v>
+      </c>
+      <c r="F254" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -5521,15 +5595,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E255" s="5">
-        <v>0</v>
-      </c>
-      <c r="F255" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E255" s="4">
+        <v>0</v>
+      </c>
+      <c r="F255" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -5540,15 +5614,15 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E256" s="5">
-        <v>0</v>
-      </c>
-      <c r="F256" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E256" s="4">
+        <v>0</v>
+      </c>
+      <c r="F256" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>255</v>
       </c>
@@ -5559,15 +5633,19 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E257" s="5">
-        <v>0</v>
-      </c>
-      <c r="F257" s="5">
+      <c r="E257" s="4">
+        <v>0</v>
+      </c>
+      <c r="F257" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G216:K218"/>
+    <mergeCell ref="G194:G195"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>